--- a/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
   <si>
     <t>PRTC</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -673,103 +673,117 @@
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F8" s="3">
         <v>8600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>7000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>11600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>5800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>6800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>15800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1900</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -809,8 +823,14 @@
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +870,14 @@
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -867,49 +893,57 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>53100</v>
+      </c>
+      <c r="F12" s="3">
         <v>67900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>84600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>62100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>48300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>43600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>38300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>40300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>45500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>44100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>33300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>36300</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -949,49 +983,61 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="F14" s="3">
         <v>8500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-55600</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-603800</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-10300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1031,8 +1077,14 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,90 +1097,104 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>17500</v>
+      </c>
+      <c r="F17" s="3">
         <v>113700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>52600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>93800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>73900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>71700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>59600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>-533300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>74700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>57200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>57300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>60300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-70000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-105100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-45600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-82200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-68100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-66800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-52800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>538700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-70300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-41400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-52300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-58400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1144,213 +1210,245 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F20" s="3">
         <v>70300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-8400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>120100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-24100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-87000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>228500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-70800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>130800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-10600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>36500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>55400</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-30200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-49700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>41600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-88600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-150300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>178900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>471800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>63300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-50200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-14800</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="E22" s="3">
-        <v>2000</v>
+        <v>1300</v>
       </c>
       <c r="F22" s="3">
         <v>2000</v>
       </c>
       <c r="G22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I22" s="3">
         <v>2700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>1200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>4200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-36800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-56000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>36000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-94900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-155500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>174500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>467400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>56300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-52400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-16100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F24" s="3">
         <v>-23200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-32500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>21100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-17400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-36400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>50800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>87300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>25100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>4300</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1390,90 +1488,108 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-13600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-23500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>14800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-77600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-119100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>123700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>380100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>31100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-54700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-16000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-7800</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-22000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-28300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>14800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-75400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-118000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>124000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>392800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>73500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-35700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-8000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>68700</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1513,8 +1629,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1554,8 +1676,14 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1595,8 +1723,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1636,90 +1770,108 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-70300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>8400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-120100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>24100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>87000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-228500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>70800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-130800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>10600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-36500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-55400</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-22000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-28300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>14800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-75400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-118000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>124000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>392800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>73500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-35700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-8000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>68700</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1759,95 +1911,113 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-22000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-28300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>14800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-75400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-118000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>124000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>392800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>73500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-35700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-8000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>68700</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1863,8 +2033,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1880,60 +2052,68 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>191100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>350500</v>
+      </c>
+      <c r="F41" s="3">
         <v>149900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>365900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>465700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>439800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>403900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>340100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>132400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>132000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>117100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>90100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>72600</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>137700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F42" s="3">
         <v>202400</v>
-      </c>
-      <c r="E42" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F42" s="3">
-        <v>2100</v>
       </c>
       <c r="G42" s="3">
         <v>2100</v>
@@ -1945,66 +2125,78 @@
         <v>2100</v>
       </c>
       <c r="J42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L42" s="3">
         <v>32200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>72200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>136000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>110300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>117000</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="F43" s="3">
         <v>22400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>9300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>23200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>6000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1800</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2044,213 +2236,249 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F45" s="3">
         <v>11600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>10800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>5400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>6000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>347200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>360100</v>
+      </c>
+      <c r="F46" s="3">
         <v>386200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>381800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>501800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>451100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>414300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>346900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>168800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>216100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>259800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>209800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>198100</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>325600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>310100</v>
+      </c>
+      <c r="F47" s="3">
         <v>278400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>399000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>398500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>403000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>531900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>714700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>727600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>324300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>169800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>213900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>131400</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>21500</v>
+      </c>
+      <c r="F48" s="3">
         <v>37200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>41400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>43900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>42000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>42900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>43200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>43800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>69800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>8300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>7600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>6900</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>900</v>
+      </c>
+      <c r="F49" s="3">
         <v>800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>7600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2290,8 +2518,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2331,49 +2565,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2413,49 +2659,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>694000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>693600</v>
+      </c>
+      <c r="F54" s="3">
         <v>702600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>823200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>946000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>896900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>990000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1105500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>941200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>618300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>441800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>434900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>339800</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2471,8 +2729,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2488,254 +2748,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F57" s="3">
         <v>26500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>15100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>35800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>39900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>21800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>12800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>19800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>21500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>15900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>12300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>16400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F58" s="3">
         <v>12500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>9500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>8700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>32200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>29700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>4400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>8500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>12000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>12400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>7500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>35000</v>
+      </c>
+      <c r="F59" s="3">
         <v>57900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>125600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>181600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>141900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>129400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>138700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>115000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>282500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>237900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>191200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>250000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>49300</v>
+      </c>
+      <c r="F60" s="3">
         <v>96900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>150300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>226100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>213900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>180900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>156000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>139200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>312600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>265800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>216000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>273900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F61" s="3">
         <v>34400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>38600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>43300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>45400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>46900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>33900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>34900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>56100</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>166100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>115400</v>
+      </c>
+      <c r="F62" s="3">
         <v>23800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>58300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>92400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>76100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>108600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>148700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>116700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>42000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>9000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>6400</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2775,8 +3073,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2816,8 +3120,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2857,49 +3167,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>229900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>179900</v>
+      </c>
+      <c r="F66" s="3">
         <v>160400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>241400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>352500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>328900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>320200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>321800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>273100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>268100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>166300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>121500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>129900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2915,8 +3237,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2956,8 +3280,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2997,8 +3327,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3038,8 +3374,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3079,49 +3421,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>212800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>250900</v>
+      </c>
+      <c r="F72" s="3">
         <v>273500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>291300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>298300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>273100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>374900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>490100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>374700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>66500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-8300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>29500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>23400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3161,8 +3515,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3202,8 +3562,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3243,49 +3609,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>464100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>513700</v>
+      </c>
+      <c r="F76" s="3">
         <v>542200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>581800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>593500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>568000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>669700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>783800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>668000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>350200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>275500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>313300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>209900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3325,95 +3703,113 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-22000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-28300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>14800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-75400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-118000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>124000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>392800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>73500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-35700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-8000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>68700</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3429,49 +3825,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F83" s="3">
         <v>4600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>4300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>3600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>3500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>3200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>3700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3511,8 +3915,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3552,8 +3962,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3593,8 +4009,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3634,8 +4056,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3675,49 +4103,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-40800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-65100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-91500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-87200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-92900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-65400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-75700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-56100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-62700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-35500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-28600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-44200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3733,49 +4173,57 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-2700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-3400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-2800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-9700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3815,8 +4263,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3856,49 +4310,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-104900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>173900</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>82400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>115000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>98400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>266100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>26700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>37000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>3500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-43200</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3914,8 +4380,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3955,8 +4423,14 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3996,8 +4470,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4037,8 +4517,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4078,57 +4564,69 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>91900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-24200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-5700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>36400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-13700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>41100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-2200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>12900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>37000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>52000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>104800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -4146,59 +4644,71 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-159400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>200600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-216000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-99800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>25900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>35900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>63800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>207800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>15000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>27000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>17400</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>PRTC</t>
   </si>
@@ -656,134 +656,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1900</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -829,8 +836,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,8 +886,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -895,55 +908,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>38900</v>
+      </c>
+      <c r="E12" s="3">
         <v>43100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>53100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>67900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>84600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>62100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>48300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>43600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>38300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>40300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>45500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>44100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>33300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>36300</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -989,8 +1006,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -998,46 +1018,49 @@
         <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-61800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-55600</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-603800</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
         <v>-10300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1083,8 +1106,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1099,102 +1125,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E17" s="3">
         <v>70200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>17500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>113700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>52600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>93800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>73900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>71700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>59600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-533300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>74700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>57200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>57300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>60300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-66400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-70000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-105100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-45600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-82200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-68100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-66800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-52800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>538700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-70300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-41400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-52300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-58400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,113 +1245,120 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E20" s="3">
         <v>49700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>70300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>120100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-24100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-87000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>228500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-70800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>130800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>36500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>55400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-30200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-49700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>41600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-88600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-150300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>178900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>471800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>63300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-50200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-14800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2000</v>
       </c>
       <c r="G22" s="3">
         <v>2000</v>
@@ -1327,128 +1367,137 @@
         <v>2000</v>
       </c>
       <c r="I22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J22" s="3">
         <v>2700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-13700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-36800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-56000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>36000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-94900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-155500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>174500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>467400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>56300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-52400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E24" s="3">
         <v>18700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-23200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-32500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-17400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-36400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>50800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>87300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>25100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1494,102 +1543,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-48900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-41100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-13600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-77600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-119100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>123700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>380100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>31100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-54700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-40700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-75400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-118000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>124000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>392800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>73500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-35700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>68700</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1635,8 +1693,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1682,8 +1743,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1729,8 +1793,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1776,102 +1843,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-49700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-70300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-120100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>24100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>87000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-228500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>70800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-130800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-36500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-55400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-40700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-75400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-118000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>124000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>392800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>73500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-35700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>68700</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1917,107 +1993,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-40700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-75400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-118000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>124000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>392800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>73500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-35700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>68700</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2035,8 +2120,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2054,69 +2140,73 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>308500</v>
+      </c>
+      <c r="E41" s="3">
         <v>191100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>350500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>149900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>365900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>465700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>439800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>403900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>340100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>132400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>132000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>117100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>90100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>72600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>193600</v>
+      </c>
+      <c r="E42" s="3">
         <v>137700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>202400</v>
-      </c>
-      <c r="G42" s="3">
-        <v>2100</v>
       </c>
       <c r="H42" s="3">
         <v>2100</v>
@@ -2131,72 +2221,78 @@
         <v>2100</v>
       </c>
       <c r="L42" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M42" s="3">
         <v>32200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>72200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>136000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>110300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>117000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E43" s="3">
         <v>14100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2242,196 +2338,211 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E45" s="3">
         <v>4300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>508800</v>
+      </c>
+      <c r="E46" s="3">
         <v>347200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>360100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>386200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>381800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>501800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>451100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>414300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>346900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>168800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>216100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>259800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>209800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>198100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E47" s="3">
         <v>325600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>310100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>278400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>399000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>398500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>403000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>531900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>714700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>727600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>324300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>169800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>213900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>131400</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E48" s="3">
         <v>19400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>37200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>42000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>42900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>43800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>69800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6900</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2442,43 +2553,46 @@
         <v>900</v>
       </c>
       <c r="F49" s="3">
+        <v>900</v>
+      </c>
+      <c r="G49" s="3">
         <v>800</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1000</v>
       </c>
       <c r="H49" s="3">
         <v>1000</v>
       </c>
       <c r="I49" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="J49" s="3">
         <v>900</v>
       </c>
       <c r="K49" s="3">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="L49" s="3">
         <v>600</v>
       </c>
       <c r="M49" s="3">
+        <v>600</v>
+      </c>
+      <c r="N49" s="3">
         <v>7600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2524,8 +2638,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2571,55 +2688,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1000</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
       </c>
       <c r="M52" s="3">
+        <v>200</v>
+      </c>
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2665,55 +2788,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>580000</v>
+      </c>
+      <c r="E54" s="3">
         <v>694000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>693600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>702600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>823200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>946000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>896900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>990000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1105500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>941200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>618300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>441800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>434900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>339800</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2731,8 +2860,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2750,232 +2880,245 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E57" s="3">
         <v>14600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>26500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>21800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>21500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>12300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16400</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E58" s="3">
         <v>7100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>9500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>32200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>29700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E59" s="3">
         <v>29600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>35000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>57900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>125600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>181600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>141900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>129400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>138700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>115000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>282500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>237900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>191200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>250000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>138300</v>
+      </c>
+      <c r="E60" s="3">
         <v>51400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>96900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>150300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>226100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>213900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>180900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>156000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>139200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>312600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>265800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>216000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>273900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E61" s="3">
         <v>18300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>20000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>34400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>38600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>43300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>45400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>46900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>33900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>34900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>56100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -2985,55 +3128,61 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E62" s="3">
         <v>166100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>115400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>58300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>92400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>76100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>108600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>148700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>116700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>42000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6400</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3079,8 +3228,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3126,8 +3278,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3173,55 +3328,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>264100</v>
+      </c>
+      <c r="E66" s="3">
         <v>229900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>179900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>160400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>241400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>352500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>328900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>320200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>321800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>273100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>268100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>166300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>121500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>129900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3239,8 +3400,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3286,8 +3448,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3333,8 +3498,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3380,8 +3548,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3427,55 +3598,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E72" s="3">
         <v>212800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>250900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>273500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>291300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>298300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>273100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>374900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>490100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>374700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>66500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>23400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3521,8 +3698,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3568,8 +3748,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3615,55 +3798,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>315900</v>
+      </c>
+      <c r="E76" s="3">
         <v>464100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>513700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>542200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>581800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>593500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>568000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>669700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>783800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>668000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>350200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>275500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>313300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>209900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3709,107 +3898,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-40700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-75400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-118000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>124000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>392800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>73500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-35700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>68700</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3827,55 +4025,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
         <v>1900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4300</v>
-      </c>
-      <c r="H83" s="3">
-        <v>3600</v>
       </c>
       <c r="I83" s="3">
         <v>3600</v>
       </c>
       <c r="J83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3921,8 +4123,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3968,8 +4173,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4015,8 +4223,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4062,8 +4273,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4109,55 +4323,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-40800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-65100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-91500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-87200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-92900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-65400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-75700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-56100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-62700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-35500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-28600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-44200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4175,55 +4395,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4269,8 +4493,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4316,55 +4543,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>236500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-104900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>173900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>82400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>115000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>98400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>266100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>26700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>37000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>3500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-43200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4382,8 +4615,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4429,8 +4663,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4476,8 +4713,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4523,8 +4763,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4570,55 +4813,61 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-39100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>91900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-24200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>36400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>41100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>37000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>52000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>104800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4650,65 +4899,71 @@
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>117400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-159400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-216000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-99800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>25900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>35900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>63800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>207800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>27000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>17400</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>PRTC</t>
   </si>
@@ -663,13 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -698,22 +696,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -745,25 +743,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>3200</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>8600</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3">
-        <v>7000</v>
+        <v>1600</v>
       </c>
       <c r="I8" s="3">
-        <v>11600</v>
+        <v>1600</v>
       </c>
       <c r="J8" s="3">
-        <v>5800</v>
+        <v>4300</v>
       </c>
       <c r="K8" s="3">
         <v>4900</v>
@@ -794,26 +792,26 @@
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F9" s="3">
+        <v>21500</v>
+      </c>
+      <c r="G9" s="3">
+        <v>21500</v>
+      </c>
+      <c r="H9" s="3">
+        <v>26600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>26600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>33900</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -844,26 +842,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-29600</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -915,25 +913,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>38900</v>
+        <v>19500</v>
       </c>
       <c r="E12" s="3">
-        <v>43100</v>
+        <v>19500</v>
       </c>
       <c r="F12" s="3">
-        <v>53100</v>
+        <v>21500</v>
       </c>
       <c r="G12" s="3">
-        <v>67900</v>
+        <v>21500</v>
       </c>
       <c r="H12" s="3">
-        <v>84600</v>
+        <v>26600</v>
       </c>
       <c r="I12" s="3">
-        <v>62100</v>
+        <v>26600</v>
       </c>
       <c r="J12" s="3">
-        <v>48300</v>
+        <v>33900</v>
       </c>
       <c r="K12" s="3">
         <v>43600</v>
@@ -1015,25 +1013,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="F14" s="3">
-        <v>-61800</v>
+        <v>-35000</v>
       </c>
       <c r="G14" s="3">
-        <v>8500</v>
+        <v>-35000</v>
       </c>
       <c r="H14" s="3">
-        <v>-55600</v>
+        <v>-34800</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-34800</v>
+      </c>
+      <c r="J14" s="3">
+        <v>5200</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1065,25 +1063,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1132,25 +1130,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>66700</v>
+        <v>33300</v>
       </c>
       <c r="E17" s="3">
-        <v>70200</v>
+        <v>33300</v>
       </c>
       <c r="F17" s="3">
-        <v>17500</v>
+        <v>35100</v>
       </c>
       <c r="G17" s="3">
-        <v>113700</v>
+        <v>35100</v>
       </c>
       <c r="H17" s="3">
+        <v>39700</v>
+      </c>
+      <c r="I17" s="3">
+        <v>39700</v>
+      </c>
+      <c r="J17" s="3">
         <v>52600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>93800</v>
-      </c>
-      <c r="J17" s="3">
-        <v>73900</v>
       </c>
       <c r="K17" s="3">
         <v>71700</v>
@@ -1182,25 +1180,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-66400</v>
+        <v>-33200</v>
       </c>
       <c r="E18" s="3">
-        <v>-70000</v>
+        <v>-33200</v>
       </c>
       <c r="F18" s="3">
-        <v>-14300</v>
+        <v>-35000</v>
       </c>
       <c r="G18" s="3">
-        <v>-105100</v>
+        <v>-35000</v>
       </c>
       <c r="H18" s="3">
-        <v>-45600</v>
+        <v>-38100</v>
       </c>
       <c r="I18" s="3">
-        <v>-82200</v>
+        <v>-38100</v>
       </c>
       <c r="J18" s="3">
-        <v>-68100</v>
+        <v>-48300</v>
       </c>
       <c r="K18" s="3">
         <v>-66800</v>
@@ -1252,25 +1250,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>12400</v>
+        <v>-3600</v>
       </c>
       <c r="E20" s="3">
-        <v>49700</v>
+        <v>-3600</v>
       </c>
       <c r="F20" s="3">
-        <v>1800</v>
+        <v>11100</v>
       </c>
       <c r="G20" s="3">
-        <v>70300</v>
+        <v>11100</v>
       </c>
       <c r="H20" s="3">
-        <v>-8400</v>
+        <v>5000</v>
       </c>
       <c r="I20" s="3">
-        <v>120100</v>
+        <v>5000</v>
       </c>
       <c r="J20" s="3">
-        <v>-24100</v>
+        <v>-33500</v>
       </c>
       <c r="K20" s="3">
         <v>-87000</v>
@@ -1302,25 +1300,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-52200</v>
+        <v>-28700</v>
       </c>
       <c r="E21" s="3">
-        <v>-18400</v>
+        <v>-28700</v>
       </c>
       <c r="F21" s="3">
-        <v>-9400</v>
+        <v>-45300</v>
       </c>
       <c r="G21" s="3">
-        <v>-30200</v>
+        <v>-45100</v>
       </c>
       <c r="H21" s="3">
-        <v>-49700</v>
+        <v>-41500</v>
       </c>
       <c r="I21" s="3">
-        <v>41600</v>
+        <v>-41500</v>
       </c>
       <c r="J21" s="3">
-        <v>-88600</v>
+        <v>-14100</v>
       </c>
       <c r="K21" s="3">
         <v>-150300</v>
@@ -1352,25 +1350,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J22" s="3">
         <v>1000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>2700</v>
       </c>
       <c r="K22" s="3">
         <v>1700</v>
@@ -1402,25 +1400,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-55000</v>
+        <v>-27500</v>
       </c>
       <c r="E23" s="3">
-        <v>-22400</v>
+        <v>-27500</v>
       </c>
       <c r="F23" s="3">
-        <v>-13700</v>
+        <v>-11200</v>
       </c>
       <c r="G23" s="3">
-        <v>-36800</v>
+        <v>-11200</v>
       </c>
       <c r="H23" s="3">
-        <v>-56000</v>
+        <v>-6900</v>
       </c>
       <c r="I23" s="3">
-        <v>36000</v>
+        <v>-6900</v>
       </c>
       <c r="J23" s="3">
-        <v>-94900</v>
+        <v>-18400</v>
       </c>
       <c r="K23" s="3">
         <v>-155500</v>
@@ -1452,25 +1450,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-6100</v>
+        <v>-3100</v>
       </c>
       <c r="E24" s="3">
-        <v>18700</v>
+        <v>-3100</v>
       </c>
       <c r="F24" s="3">
-        <v>11800</v>
+        <v>9400</v>
       </c>
       <c r="G24" s="3">
-        <v>-23200</v>
+        <v>9400</v>
       </c>
       <c r="H24" s="3">
-        <v>-32500</v>
+        <v>5900</v>
       </c>
       <c r="I24" s="3">
-        <v>21100</v>
+        <v>5900</v>
       </c>
       <c r="J24" s="3">
-        <v>-17400</v>
+        <v>-11600</v>
       </c>
       <c r="K24" s="3">
         <v>-36400</v>
@@ -1552,25 +1550,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-48900</v>
+        <v>-24400</v>
       </c>
       <c r="E26" s="3">
-        <v>-41100</v>
+        <v>-24400</v>
       </c>
       <c r="F26" s="3">
-        <v>-25600</v>
+        <v>-20500</v>
       </c>
       <c r="G26" s="3">
-        <v>-13600</v>
+        <v>-20500</v>
       </c>
       <c r="H26" s="3">
-        <v>-23500</v>
+        <v>-12800</v>
       </c>
       <c r="I26" s="3">
-        <v>14800</v>
+        <v>-12800</v>
       </c>
       <c r="J26" s="3">
-        <v>-77600</v>
+        <v>-6800</v>
       </c>
       <c r="K26" s="3">
         <v>-119100</v>
@@ -1602,25 +1600,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-41800</v>
+        <v>-20900</v>
       </c>
       <c r="E27" s="3">
-        <v>-40700</v>
+        <v>-20900</v>
       </c>
       <c r="F27" s="3">
-        <v>-25000</v>
+        <v>-20300</v>
       </c>
       <c r="G27" s="3">
-        <v>-22000</v>
+        <v>-20300</v>
       </c>
       <c r="H27" s="3">
-        <v>-28300</v>
+        <v>-12500</v>
       </c>
       <c r="I27" s="3">
-        <v>14800</v>
+        <v>-12500</v>
       </c>
       <c r="J27" s="3">
-        <v>-75400</v>
+        <v>-11000</v>
       </c>
       <c r="K27" s="3">
         <v>-118000</v>
@@ -1852,25 +1850,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-12400</v>
+        <v>3600</v>
       </c>
       <c r="E32" s="3">
-        <v>-49700</v>
+        <v>3600</v>
       </c>
       <c r="F32" s="3">
-        <v>-1800</v>
+        <v>-11100</v>
       </c>
       <c r="G32" s="3">
-        <v>-70300</v>
+        <v>-11100</v>
       </c>
       <c r="H32" s="3">
-        <v>8400</v>
+        <v>-5000</v>
       </c>
       <c r="I32" s="3">
-        <v>-120100</v>
+        <v>-5000</v>
       </c>
       <c r="J32" s="3">
-        <v>24100</v>
+        <v>33500</v>
       </c>
       <c r="K32" s="3">
         <v>87000</v>
@@ -1902,25 +1900,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-41800</v>
+        <v>-20900</v>
       </c>
       <c r="E33" s="3">
-        <v>-40700</v>
+        <v>-20900</v>
       </c>
       <c r="F33" s="3">
-        <v>-25000</v>
+        <v>-20300</v>
       </c>
       <c r="G33" s="3">
-        <v>-22000</v>
+        <v>-20300</v>
       </c>
       <c r="H33" s="3">
-        <v>-28300</v>
+        <v>-12500</v>
       </c>
       <c r="I33" s="3">
-        <v>14800</v>
+        <v>-12500</v>
       </c>
       <c r="J33" s="3">
-        <v>-75400</v>
+        <v>-11000</v>
       </c>
       <c r="K33" s="3">
         <v>-118000</v>
@@ -2002,25 +2000,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-41800</v>
+        <v>-20900</v>
       </c>
       <c r="E35" s="3">
-        <v>-40700</v>
+        <v>-20900</v>
       </c>
       <c r="F35" s="3">
-        <v>-25000</v>
+        <v>-20300</v>
       </c>
       <c r="G35" s="3">
-        <v>-22000</v>
+        <v>-20300</v>
       </c>
       <c r="H35" s="3">
-        <v>-28300</v>
+        <v>-12500</v>
       </c>
       <c r="I35" s="3">
-        <v>14800</v>
+        <v>-12500</v>
       </c>
       <c r="J35" s="3">
-        <v>-75400</v>
+        <v>-11000</v>
       </c>
       <c r="K35" s="3">
         <v>-118000</v>
@@ -2060,22 +2058,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -2150,22 +2148,22 @@
         <v>308500</v>
       </c>
       <c r="E41" s="3">
+        <v>308500</v>
+      </c>
+      <c r="F41" s="3">
         <v>191100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>191100</v>
+      </c>
+      <c r="H41" s="3">
         <v>350500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>350500</v>
+      </c>
+      <c r="J41" s="3">
         <v>149900</v>
-      </c>
-      <c r="H41" s="3">
-        <v>365900</v>
-      </c>
-      <c r="I41" s="3">
-        <v>465700</v>
-      </c>
-      <c r="J41" s="3">
-        <v>439800</v>
       </c>
       <c r="K41" s="3">
         <v>403900</v>
@@ -2197,25 +2195,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>193600</v>
+        <v>191900</v>
       </c>
       <c r="E42" s="3">
-        <v>137700</v>
+        <v>191900</v>
       </c>
       <c r="F42" s="3">
-        <v>1600</v>
+        <v>136100</v>
       </c>
       <c r="G42" s="3">
-        <v>202400</v>
+        <v>136100</v>
       </c>
       <c r="H42" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>2100</v>
+        <v>200200</v>
       </c>
       <c r="K42" s="3">
         <v>2100</v>
@@ -2250,22 +2248,22 @@
         <v>2100</v>
       </c>
       <c r="E43" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F43" s="3">
         <v>14100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
+        <v>14100</v>
+      </c>
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J43" s="3">
         <v>22400</v>
-      </c>
-      <c r="H43" s="3">
-        <v>9300</v>
-      </c>
-      <c r="I43" s="3">
-        <v>23200</v>
-      </c>
-      <c r="J43" s="3">
-        <v>3800</v>
       </c>
       <c r="K43" s="3">
         <v>2900</v>
@@ -2296,26 +2294,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2347,25 +2345,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4700</v>
+        <v>1600</v>
       </c>
       <c r="E45" s="3">
-        <v>4300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>11600</v>
+        <v>1600</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
-        <v>4500</v>
+        <v>1600</v>
       </c>
       <c r="I45" s="3">
-        <v>10800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>5300</v>
+        <v>1600</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>5400</v>
@@ -2400,22 +2398,22 @@
         <v>508800</v>
       </c>
       <c r="E46" s="3">
+        <v>508800</v>
+      </c>
+      <c r="F46" s="3">
         <v>347200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>347200</v>
+      </c>
+      <c r="H46" s="3">
         <v>360100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>360100</v>
+      </c>
+      <c r="J46" s="3">
         <v>386200</v>
-      </c>
-      <c r="H46" s="3">
-        <v>381800</v>
-      </c>
-      <c r="I46" s="3">
-        <v>501800</v>
-      </c>
-      <c r="J46" s="3">
-        <v>451100</v>
       </c>
       <c r="K46" s="3">
         <v>414300</v>
@@ -2450,22 +2448,22 @@
         <v>45200</v>
       </c>
       <c r="E47" s="3">
+        <v>45200</v>
+      </c>
+      <c r="F47" s="3">
         <v>325600</v>
       </c>
-      <c r="F47" s="3">
-        <v>310100</v>
-      </c>
       <c r="G47" s="3">
-        <v>278400</v>
+        <v>325600</v>
       </c>
       <c r="H47" s="3">
-        <v>399000</v>
+        <v>309900</v>
       </c>
       <c r="I47" s="3">
-        <v>398500</v>
+        <v>309900</v>
       </c>
       <c r="J47" s="3">
-        <v>403000</v>
+        <v>277500</v>
       </c>
       <c r="K47" s="3">
         <v>531900</v>
@@ -2500,22 +2498,22 @@
         <v>17300</v>
       </c>
       <c r="E48" s="3">
+        <v>17300</v>
+      </c>
+      <c r="F48" s="3">
         <v>19400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>19400</v>
+      </c>
+      <c r="H48" s="3">
         <v>21500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>21500</v>
+      </c>
+      <c r="J48" s="3">
         <v>37200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>41400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>43900</v>
-      </c>
-      <c r="J48" s="3">
-        <v>42000</v>
       </c>
       <c r="K48" s="3">
         <v>42900</v>
@@ -2556,16 +2554,16 @@
         <v>900</v>
       </c>
       <c r="G49" s="3">
+        <v>900</v>
+      </c>
+      <c r="H49" s="3">
+        <v>900</v>
+      </c>
+      <c r="I49" s="3">
+        <v>900</v>
+      </c>
+      <c r="J49" s="3">
         <v>800</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>900</v>
       </c>
       <c r="K49" s="3">
         <v>900</v>
@@ -2697,22 +2695,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7700</v>
+        <v>900</v>
       </c>
       <c r="E52" s="3">
         <v>900</v>
       </c>
       <c r="F52" s="3">
+        <v>900</v>
+      </c>
+      <c r="G52" s="3">
+        <v>900</v>
+      </c>
+      <c r="H52" s="3">
         <v>1000</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
       <c r="I52" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="J52" s="3">
         <v>0</v>
@@ -2800,22 +2798,22 @@
         <v>580000</v>
       </c>
       <c r="E54" s="3">
+        <v>580000</v>
+      </c>
+      <c r="F54" s="3">
         <v>694000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>694000</v>
+      </c>
+      <c r="H54" s="3">
         <v>693600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>693600</v>
+      </c>
+      <c r="J54" s="3">
         <v>702600</v>
-      </c>
-      <c r="H54" s="3">
-        <v>823200</v>
-      </c>
-      <c r="I54" s="3">
-        <v>946000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>896900</v>
       </c>
       <c r="K54" s="3">
         <v>990000</v>
@@ -2890,22 +2888,22 @@
         <v>8100</v>
       </c>
       <c r="E57" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F57" s="3">
         <v>14600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
+        <v>14600</v>
+      </c>
+      <c r="H57" s="3">
         <v>8700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J57" s="3">
         <v>26500</v>
-      </c>
-      <c r="H57" s="3">
-        <v>15100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>35800</v>
-      </c>
-      <c r="J57" s="3">
-        <v>39900</v>
       </c>
       <c r="K57" s="3">
         <v>21800</v>
@@ -2937,25 +2935,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7600</v>
+        <v>10900</v>
       </c>
       <c r="E58" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F58" s="3">
         <v>7100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H58" s="3">
         <v>5600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J58" s="3">
         <v>12500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>9500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>8700</v>
-      </c>
-      <c r="J58" s="3">
-        <v>32200</v>
       </c>
       <c r="K58" s="3">
         <v>29700</v>
@@ -2987,25 +2985,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>122600</v>
+        <v>96000</v>
       </c>
       <c r="E59" s="3">
-        <v>29600</v>
+        <v>96000</v>
       </c>
       <c r="F59" s="3">
-        <v>35000</v>
+        <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>57900</v>
+        <v>200</v>
       </c>
       <c r="H59" s="3">
-        <v>125600</v>
+        <v>12400</v>
       </c>
       <c r="I59" s="3">
-        <v>181600</v>
+        <v>12400</v>
       </c>
       <c r="J59" s="3">
-        <v>141900</v>
+        <v>31600</v>
       </c>
       <c r="K59" s="3">
         <v>129400</v>
@@ -3040,22 +3038,22 @@
         <v>138300</v>
       </c>
       <c r="E60" s="3">
+        <v>138300</v>
+      </c>
+      <c r="F60" s="3">
         <v>51400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>51400</v>
+      </c>
+      <c r="H60" s="3">
         <v>49300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>49300</v>
+      </c>
+      <c r="J60" s="3">
         <v>96900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>150300</v>
-      </c>
-      <c r="I60" s="3">
-        <v>226100</v>
-      </c>
-      <c r="J60" s="3">
-        <v>213900</v>
       </c>
       <c r="K60" s="3">
         <v>180900</v>
@@ -3087,25 +3085,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16400</v>
+        <v>133900</v>
       </c>
       <c r="E61" s="3">
-        <v>18300</v>
+        <v>133900</v>
       </c>
       <c r="F61" s="3">
-        <v>20000</v>
+        <v>128400</v>
       </c>
       <c r="G61" s="3">
+        <v>128400</v>
+      </c>
+      <c r="H61" s="3">
+        <v>123700</v>
+      </c>
+      <c r="I61" s="3">
+        <v>123700</v>
+      </c>
+      <c r="J61" s="3">
         <v>34400</v>
-      </c>
-      <c r="H61" s="3">
-        <v>38600</v>
-      </c>
-      <c r="I61" s="3">
-        <v>43300</v>
-      </c>
-      <c r="J61" s="3">
-        <v>45400</v>
       </c>
       <c r="K61" s="3">
         <v>46900</v>
@@ -3137,25 +3135,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>119000</v>
+        <v>1600</v>
       </c>
       <c r="E62" s="3">
-        <v>166100</v>
+        <v>1600</v>
       </c>
       <c r="F62" s="3">
-        <v>115400</v>
+        <v>3500</v>
       </c>
       <c r="G62" s="3">
-        <v>23800</v>
+        <v>3500</v>
       </c>
       <c r="H62" s="3">
-        <v>58300</v>
+        <v>2600</v>
       </c>
       <c r="I62" s="3">
-        <v>92400</v>
+        <v>2600</v>
       </c>
       <c r="J62" s="3">
-        <v>76100</v>
+        <v>4100</v>
       </c>
       <c r="K62" s="3">
         <v>108600</v>
@@ -3337,25 +3335,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>264100</v>
+        <v>273700</v>
       </c>
       <c r="E66" s="3">
-        <v>229900</v>
+        <v>273700</v>
       </c>
       <c r="F66" s="3">
-        <v>179900</v>
+        <v>235700</v>
       </c>
       <c r="G66" s="3">
-        <v>160400</v>
+        <v>235700</v>
       </c>
       <c r="H66" s="3">
-        <v>241400</v>
+        <v>184700</v>
       </c>
       <c r="I66" s="3">
-        <v>352500</v>
+        <v>184700</v>
       </c>
       <c r="J66" s="3">
-        <v>328900</v>
+        <v>155100</v>
       </c>
       <c r="K66" s="3">
         <v>320200</v>
@@ -3607,25 +3605,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>67500</v>
+        <v>-62500</v>
       </c>
       <c r="E72" s="3">
-        <v>212800</v>
+        <v>-62500</v>
       </c>
       <c r="F72" s="3">
-        <v>250900</v>
+        <v>83800</v>
       </c>
       <c r="G72" s="3">
-        <v>273500</v>
+        <v>83800</v>
       </c>
       <c r="H72" s="3">
-        <v>291300</v>
+        <v>124500</v>
       </c>
       <c r="I72" s="3">
-        <v>298300</v>
+        <v>124500</v>
       </c>
       <c r="J72" s="3">
-        <v>273100</v>
+        <v>149500</v>
       </c>
       <c r="K72" s="3">
         <v>374900</v>
@@ -3810,22 +3808,22 @@
         <v>315900</v>
       </c>
       <c r="E76" s="3">
+        <v>315900</v>
+      </c>
+      <c r="F76" s="3">
         <v>464100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>464100</v>
+      </c>
+      <c r="H76" s="3">
         <v>513700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>513700</v>
+      </c>
+      <c r="J76" s="3">
         <v>542200</v>
-      </c>
-      <c r="H76" s="3">
-        <v>581800</v>
-      </c>
-      <c r="I76" s="3">
-        <v>593500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>568000</v>
       </c>
       <c r="K76" s="3">
         <v>669700</v>
@@ -3915,22 +3913,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -3962,25 +3960,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-41800</v>
+        <v>-20900</v>
       </c>
       <c r="E81" s="3">
-        <v>-40700</v>
+        <v>-20900</v>
       </c>
       <c r="F81" s="3">
-        <v>-25000</v>
+        <v>-20300</v>
       </c>
       <c r="G81" s="3">
-        <v>-22000</v>
+        <v>-20300</v>
       </c>
       <c r="H81" s="3">
-        <v>-28300</v>
+        <v>-12500</v>
       </c>
       <c r="I81" s="3">
-        <v>14800</v>
+        <v>-12500</v>
       </c>
       <c r="J81" s="3">
-        <v>-75400</v>
+        <v>-11000</v>
       </c>
       <c r="K81" s="3">
         <v>-118000</v>
@@ -4032,25 +4030,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="J83" s="3">
         <v>1800</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4600</v>
-      </c>
-      <c r="H83" s="3">
-        <v>4300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>3600</v>
-      </c>
-      <c r="J83" s="3">
-        <v>3600</v>
       </c>
       <c r="K83" s="3">
         <v>3500</v>
@@ -4332,25 +4330,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-80000</v>
+        <v>-40000</v>
       </c>
       <c r="E89" s="3">
-        <v>-40800</v>
+        <v>-40000</v>
       </c>
       <c r="F89" s="3">
-        <v>-65100</v>
+        <v>-20400</v>
       </c>
       <c r="G89" s="3">
-        <v>-91500</v>
+        <v>-20400</v>
       </c>
       <c r="H89" s="3">
-        <v>-87200</v>
+        <v>-32600</v>
       </c>
       <c r="I89" s="3">
-        <v>-92900</v>
+        <v>-32600</v>
       </c>
       <c r="J89" s="3">
-        <v>-65400</v>
+        <v>-45800</v>
       </c>
       <c r="K89" s="3">
         <v>-75700</v>
@@ -4401,26 +4399,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-200</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-2900</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-2700</v>
+        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-3400</v>
@@ -4552,25 +4550,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>236500</v>
+        <v>118300</v>
       </c>
       <c r="E94" s="3">
-        <v>-104900</v>
+        <v>118300</v>
       </c>
       <c r="F94" s="3">
-        <v>173900</v>
+        <v>-52400</v>
       </c>
       <c r="G94" s="3">
-        <v>-100300</v>
+        <v>-52400</v>
       </c>
       <c r="H94" s="3">
-        <v>-6900</v>
+        <v>86900</v>
       </c>
       <c r="I94" s="3">
-        <v>82400</v>
+        <v>86900</v>
       </c>
       <c r="J94" s="3">
-        <v>115000</v>
+        <v>-50200</v>
       </c>
       <c r="K94" s="3">
         <v>98400</v>
@@ -4621,26 +4619,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4822,25 +4820,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-39100</v>
+        <v>-19600</v>
       </c>
       <c r="E100" s="3">
-        <v>-13800</v>
+        <v>-19600</v>
       </c>
       <c r="F100" s="3">
-        <v>91900</v>
+        <v>-6900</v>
       </c>
       <c r="G100" s="3">
-        <v>-24200</v>
+        <v>-6900</v>
       </c>
       <c r="H100" s="3">
-        <v>-5700</v>
+        <v>45900</v>
       </c>
       <c r="I100" s="3">
-        <v>36400</v>
+        <v>45900</v>
       </c>
       <c r="J100" s="3">
-        <v>-13700</v>
+        <v>-12100</v>
       </c>
       <c r="K100" s="3">
         <v>41100</v>
@@ -4871,26 +4869,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4922,25 +4920,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>117400</v>
+        <v>58700</v>
       </c>
       <c r="E102" s="3">
-        <v>-159400</v>
+        <v>58700</v>
       </c>
       <c r="F102" s="3">
-        <v>200600</v>
+        <v>-79700</v>
       </c>
       <c r="G102" s="3">
-        <v>-216000</v>
+        <v>-79700</v>
       </c>
       <c r="H102" s="3">
-        <v>-99800</v>
+        <v>100300</v>
       </c>
       <c r="I102" s="3">
-        <v>25900</v>
+        <v>100300</v>
       </c>
       <c r="J102" s="3">
-        <v>35900</v>
+        <v>-108000</v>
       </c>
       <c r="K102" s="3">
         <v>63800</v>

--- a/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>PRTC</t>
   </si>
@@ -656,97 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43281</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43100</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>100</v>
+        <v>2300</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>2300</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
@@ -755,70 +762,76 @@
         <v>100</v>
       </c>
       <c r="H8" s="3">
+        <v>100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>100</v>
+      </c>
+      <c r="J8" s="3">
         <v>1600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>6800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>15800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1900</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>15200</v>
+      </c>
+      <c r="F9" s="3">
         <v>19500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>19500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>21500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>21500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>26600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>26600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>33900</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -837,38 +850,44 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="F10" s="3">
         <v>-19300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-19300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-21500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-21500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-25000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-25000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-29600</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -887,8 +906,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,58 +932,66 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F12" s="3">
         <v>19500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>19500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>21500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>21500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>26600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>26600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>33900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>43600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>38300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>40300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>45500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>44100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>33300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>36300</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1007,88 +1040,100 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-2000</v>
+        <v>-73600</v>
       </c>
       <c r="E14" s="3">
-        <v>-2000</v>
+        <v>-73600</v>
       </c>
       <c r="F14" s="3">
-        <v>-35000</v>
+        <v>-7800</v>
       </c>
       <c r="G14" s="3">
-        <v>-35000</v>
+        <v>-7800</v>
       </c>
       <c r="H14" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-31800</v>
+      </c>
+      <c r="K14" s="3">
         <v>-34800</v>
       </c>
-      <c r="I14" s="3">
-        <v>-34800</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>5200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-603800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-10300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>600</v>
+      </c>
+      <c r="F15" s="3">
         <v>900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>1500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>1500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1107,8 +1152,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,108 +1175,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F17" s="3">
         <v>33300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>33300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>35100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>35100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>39700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>39700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>52600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>71700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>59600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>-533300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>74700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>57200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>57300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>60300</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-34700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-33200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-33200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-35000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-35000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-38100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-38100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-48300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-66800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-52800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>538700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-70300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-41400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-52300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-58400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,258 +1309,290 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3600</v>
+        <v>5700</v>
       </c>
       <c r="E20" s="3">
-        <v>-3600</v>
+        <v>5700</v>
       </c>
       <c r="F20" s="3">
-        <v>11100</v>
+        <v>2200</v>
       </c>
       <c r="G20" s="3">
-        <v>11100</v>
+        <v>2200</v>
       </c>
       <c r="H20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="I20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-33500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-87000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>228500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-70800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>130800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-10600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>36500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>55400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-28700</v>
+        <v>-40000</v>
       </c>
       <c r="E21" s="3">
-        <v>-28700</v>
+        <v>-39900</v>
       </c>
       <c r="F21" s="3">
-        <v>-45300</v>
+        <v>-34500</v>
       </c>
       <c r="G21" s="3">
-        <v>-45100</v>
+        <v>-34500</v>
       </c>
       <c r="H21" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-31300</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="K21" s="3">
         <v>-41500</v>
       </c>
-      <c r="I21" s="3">
-        <v>-41500</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-14100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-150300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>178900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>471800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>63300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-50200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E22" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F22" s="3">
         <v>5800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>5800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>4300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>4300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>2500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>1700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>1200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>4200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>500</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>39400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-27500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-27500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-11200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-6900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-18400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-155500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>174500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>467400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>56300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-52400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3500</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F24" s="3">
         <v>-3100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-3100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>9400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>9400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>5900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>5900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-11600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-36400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>50800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>87300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>25100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>4300</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,108 +1641,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>38300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-24400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-24400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-20500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-20500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-12800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-12800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-6800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-119100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>123700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>380100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>31100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-54700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7800</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>47600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-20900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-20900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-20300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-20300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-12500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-12500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-11000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-118000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>124000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>392800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>73500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-35700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>68700</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,8 +1809,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1744,8 +1865,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1921,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,108 +1977,126 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3600</v>
+        <v>-5700</v>
       </c>
       <c r="E32" s="3">
-        <v>3600</v>
+        <v>-5700</v>
       </c>
       <c r="F32" s="3">
-        <v>-11100</v>
+        <v>-2200</v>
       </c>
       <c r="G32" s="3">
-        <v>-11100</v>
+        <v>-2200</v>
       </c>
       <c r="H32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="I32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>33500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>87000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-228500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>70800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-130800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>10600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-36500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-55400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>47600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-20900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-20900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-20300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-20300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-12500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-12500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-11000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-118000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>124000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>392800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>73500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-35700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>68700</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,113 +2145,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>47600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-20900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-20900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-20300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-20300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-12500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-12500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-11000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-118000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>124000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>392800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>73500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-35700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>68700</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43281</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43100</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2288,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,158 +2310,178 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>280600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>280600</v>
+      </c>
+      <c r="F41" s="3">
         <v>308500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>308500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>191100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>191100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>350500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>350500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>149900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>403900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>340100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>132400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>132000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>117100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>90100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>72600</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>98000</v>
+      </c>
+      <c r="F42" s="3">
         <v>191900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>191900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>136100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>136100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>200200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>2100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>32200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>72200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>136000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>110300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>117000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F43" s="3">
         <v>2100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>14100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>14100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>22400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>6000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1800</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2315,11 +2506,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2339,216 +2530,246 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1600</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>5400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>5900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>6000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>6600</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>386300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>386300</v>
+      </c>
+      <c r="F46" s="3">
         <v>508800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>508800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>347200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>347200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>360100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>360100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>386200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>414300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>346900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>168800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>216100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>259800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>209800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>198100</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>200200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>200200</v>
+      </c>
+      <c r="F47" s="3">
         <v>45200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>45200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>325600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>325600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>309900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>309900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>277500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>531900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>714700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>727600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>324300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>169800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>213900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>131400</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>15100</v>
+      </c>
+      <c r="F48" s="3">
         <v>17300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>17300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>19400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>19400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>21500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>21500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>37200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>42900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>43200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>43800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>69800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>8300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>7600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6900</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="E49" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="F49" s="3">
         <v>900</v>
@@ -2563,34 +2784,40 @@
         <v>900</v>
       </c>
       <c r="J49" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="K49" s="3">
         <v>900</v>
       </c>
       <c r="L49" s="3">
+        <v>800</v>
+      </c>
+      <c r="M49" s="3">
+        <v>900</v>
+      </c>
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>7600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3300</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2866,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,16 +2922,22 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="E52" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="F52" s="3">
         <v>900</v>
@@ -2707,40 +2946,46 @@
         <v>900</v>
       </c>
       <c r="H52" s="3">
+        <v>900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>900</v>
+      </c>
+      <c r="J52" s="3">
         <v>1000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,58 +3034,70 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>602600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>602600</v>
+      </c>
+      <c r="F54" s="3">
         <v>580000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>580000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>694000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>694000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>693600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>693600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>702600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>990000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1105500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>941200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>618300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>441800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>434900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>339800</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +3116,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,308 +3138,346 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F57" s="3">
         <v>8100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>8100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>14600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>8700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>26500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>21800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>12800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>19800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>21500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>15900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>12300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>16400</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>14100</v>
+      </c>
+      <c r="F58" s="3">
         <v>10900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>10900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>7100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>12500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>29700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>4500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>4400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>8500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>12000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>12400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>7500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F59" s="3">
         <v>96000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>96000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>12400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>12400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>31600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>129400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>138700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>115000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>282500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>237900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>191200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>250000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>41400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>41400</v>
+      </c>
+      <c r="F60" s="3">
         <v>138300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>138300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>51400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>51400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>49300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>49300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>96900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>180900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>156000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>139200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>312600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>265800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>216000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>273900</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>151500</v>
+      </c>
+      <c r="F61" s="3">
         <v>133900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>133900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>128400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>128400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>123700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>123700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>34400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>46900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>33900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>34900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>56100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F62" s="3">
         <v>1600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>2600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>4100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>108600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>148700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>116700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>42000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>9000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>6400</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3526,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3582,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,58 +3638,70 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>194700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>194700</v>
+      </c>
+      <c r="F66" s="3">
         <v>273700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>273700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>235700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>235700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>184700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>184700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>155100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>320200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>321800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>273100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>268100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>166300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>121500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>129900</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3720,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3772,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3828,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3549,8 +3884,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,58 +3940,70 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>32500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-62500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-62500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>83800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>83800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>124500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>124500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>149500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>374900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>490100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>374700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>66500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-8300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>29500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>23400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +4052,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +4108,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,58 +4164,70 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>414700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>414700</v>
+      </c>
+      <c r="F76" s="3">
         <v>315900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>315900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>464100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>464100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>513700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>513700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>542200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>669700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>783800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>668000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>350200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>275500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>313300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>209900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,113 +4276,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43281</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43100</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>47600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-20900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-20900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-20300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-20300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-12500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-12500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-11000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-118000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>124000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>392800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>73500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-35700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>68700</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,58 +4419,66 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>900</v>
+      </c>
+      <c r="F83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>2100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>2100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>3200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>3700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>2900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4527,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4583,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4639,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4695,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,58 +4751,70 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="F89" s="3">
         <v>-40000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-40000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-20400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-20400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-32600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-32600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-45800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-75700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-56100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-62700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-35500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-28600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-44200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,22 +4833,24 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -4418,34 +4859,40 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-9700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4941,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,58 +4997,70 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F94" s="3">
         <v>118300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>118300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-52400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-52400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>86900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>86900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-50200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>98400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>266100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>26700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>37000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>3500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-43200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,8 +5079,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4640,11 +5107,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4664,8 +5131,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +5187,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5243,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,58 +5299,70 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-19600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-19600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-6900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-6900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>45900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>45900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-12100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>41100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>12900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>37000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>52000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>104800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4890,78 +5387,90 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="F102" s="3">
         <v>58700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>58700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-79700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-79700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>100300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>100300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-108000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>63800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>207800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>15000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>27000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>17400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRTC_QTR_FIN.xlsx
@@ -818,10 +818,10 @@
         <v>19500</v>
       </c>
       <c r="H9" s="3">
-        <v>21500</v>
+        <v>20900</v>
       </c>
       <c r="I9" s="3">
-        <v>21500</v>
+        <v>20900</v>
       </c>
       <c r="J9" s="3">
         <v>26600</v>
@@ -874,10 +874,10 @@
         <v>-19300</v>
       </c>
       <c r="H10" s="3">
-        <v>-21500</v>
+        <v>-20800</v>
       </c>
       <c r="I10" s="3">
-        <v>-21500</v>
+        <v>-20800</v>
       </c>
       <c r="J10" s="3">
         <v>-25000</v>
@@ -1052,10 +1052,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-73600</v>
+        <v>-67100</v>
       </c>
       <c r="E14" s="3">
-        <v>-73600</v>
+        <v>-67100</v>
       </c>
       <c r="F14" s="3">
         <v>-7800</v>
@@ -1064,10 +1064,10 @@
         <v>-7800</v>
       </c>
       <c r="H14" s="3">
-        <v>-21200</v>
+        <v>-37400</v>
       </c>
       <c r="I14" s="3">
-        <v>-21200</v>
+        <v>-37400</v>
       </c>
       <c r="J14" s="3">
         <v>-31800</v>
@@ -1195,10 +1195,10 @@
         <v>33300</v>
       </c>
       <c r="H17" s="3">
-        <v>35100</v>
+        <v>34500</v>
       </c>
       <c r="I17" s="3">
-        <v>35100</v>
+        <v>34500</v>
       </c>
       <c r="J17" s="3">
         <v>39700</v>
@@ -1251,10 +1251,10 @@
         <v>-33200</v>
       </c>
       <c r="H18" s="3">
-        <v>-35000</v>
+        <v>-34400</v>
       </c>
       <c r="I18" s="3">
-        <v>-35000</v>
+        <v>-34400</v>
       </c>
       <c r="J18" s="3">
         <v>-38100</v>
@@ -1317,10 +1317,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5700</v>
+        <v>-800</v>
       </c>
       <c r="E20" s="3">
-        <v>5700</v>
+        <v>-800</v>
       </c>
       <c r="F20" s="3">
         <v>2200</v>
@@ -1329,10 +1329,10 @@
         <v>2200</v>
       </c>
       <c r="H20" s="3">
-        <v>-2800</v>
+        <v>14100</v>
       </c>
       <c r="I20" s="3">
-        <v>-2800</v>
+        <v>14100</v>
       </c>
       <c r="J20" s="3">
         <v>1900</v>
@@ -1373,10 +1373,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-40000</v>
+        <v>-33500</v>
       </c>
       <c r="E21" s="3">
-        <v>-39900</v>
+        <v>-33300</v>
       </c>
       <c r="F21" s="3">
         <v>-34500</v>
@@ -1385,10 +1385,10 @@
         <v>-34500</v>
       </c>
       <c r="H21" s="3">
-        <v>-31500</v>
+        <v>-47700</v>
       </c>
       <c r="I21" s="3">
-        <v>-31300</v>
+        <v>-47500</v>
       </c>
       <c r="J21" s="3">
         <v>-38500</v>
@@ -1989,10 +1989,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5700</v>
+        <v>800</v>
       </c>
       <c r="E32" s="3">
-        <v>-5700</v>
+        <v>800</v>
       </c>
       <c r="F32" s="3">
         <v>-2200</v>
@@ -2001,10 +2001,10 @@
         <v>-2200</v>
       </c>
       <c r="H32" s="3">
-        <v>2800</v>
+        <v>-14100</v>
       </c>
       <c r="I32" s="3">
-        <v>2800</v>
+        <v>-14100</v>
       </c>
       <c r="J32" s="3">
         <v>-1900</v>
